--- a/tests/fixtures/golden.xlsx
+++ b/tests/fixtures/golden.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预期检查" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="测试数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="使用说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="预期检查" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试数据'!$A$1:$E$16</definedName>
@@ -923,7 +923,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>这是一份 SmartSheet AI 的脱敏演示数据，可直接上传测试。所有姓名、联系方式标识和订单号均为虚构。</t>
+          <t>这是一份 E-commerce Lead Automation 的脱敏合成演示数据，可直接上传测试。所有姓名、联系方式标识和订单号均为虚构。</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>点击“下载完整结果”，应得到“全部结果 / 高意向 / 待复核 / 使用说明”四个工作表。</t>
+          <t>点击“下载全部结果（草稿）”，应得到“全部结果 / 高意向 / 待复核 / 使用说明”四个工作表。</t>
         </is>
       </c>
     </row>
